--- a/data/trans_dic/P1428-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1428-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,18</t>
+          <t>2,9; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,36</t>
+          <t>2,1; 6,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,74</t>
+          <t>0,82; 3,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,9</t>
+          <t>2,67; 5,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,28</t>
+          <t>6,58; 13,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,45</t>
+          <t>2,89; 8,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,9</t>
+          <t>2,96; 8,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,12</t>
+          <t>6,05; 10,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,55</t>
+          <t>4,95; 8,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,26</t>
+          <t>2,79; 6,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,82</t>
+          <t>2,12; 4,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,33</t>
+          <t>4,65; 7,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,9</t>
+          <t>2,21; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,45</t>
+          <t>2,26; 6,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,3</t>
+          <t>1,49; 5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,21</t>
+          <t>2,66; 6,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,2</t>
+          <t>4,1; 9,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,35</t>
+          <t>2,46; 7,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,23</t>
+          <t>2,1; 6,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,68</t>
+          <t>7,92; 12,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,98</t>
+          <t>3,57; 7,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,01</t>
+          <t>2,88; 5,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,16</t>
+          <t>2,09; 5,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,67</t>
+          <t>5,7; 8,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,03</t>
+          <t>4,96; 9,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,9</t>
+          <t>5,2; 9,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,16</t>
+          <t>1,96; 5,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,01</t>
+          <t>3,99; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 26,72</t>
+          <t>14,09; 26,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 19,88</t>
+          <t>10,28; 19,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,93; 20,96</t>
+          <t>8,82; 21,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 21,28</t>
+          <t>11,81; 21,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,4</t>
+          <t>7,86; 12,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,65</t>
+          <t>7,6; 11,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,92</t>
+          <t>4,11; 7,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,48</t>
+          <t>6,81; 11,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,33</t>
+          <t>9,03; 12,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,38</t>
+          <t>4,42; 7,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,18</t>
+          <t>3,66; 6,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,04</t>
+          <t>5,52; 8,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 16,58</t>
+          <t>11,38; 16,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,63</t>
+          <t>4,18; 7,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,16</t>
+          <t>3,87; 7,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 61,91</t>
+          <t>9,27; 12,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,13</t>
+          <t>10,5; 13,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 6,86</t>
+          <t>4,76; 7,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,19</t>
+          <t>4,1; 6,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 42,18</t>
+          <t>7,34; 9,55</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,62</t>
+          <t>5,79; 11,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,54</t>
+          <t>3,57; 7,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,49</t>
+          <t>3,21; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,32</t>
+          <t>4,39; 8,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,0</t>
+          <t>14,94; 21,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,37</t>
+          <t>12,33; 17,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,04</t>
+          <t>10,05; 15,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 21,13</t>
+          <t>16,88; 21,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,66</t>
+          <t>12,06; 16,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,94</t>
+          <t>9,36; 12,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 10,44</t>
+          <t>7,39; 10,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,98</t>
+          <t>12,15; 15,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,79</t>
+          <t>0,26; 2,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,72</t>
+          <t>0,37; 3,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,67; 27,43</t>
+          <t>22,36; 27,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,04</t>
+          <t>17,16; 22,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,44</t>
+          <t>10,94; 15,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,49; 21,96</t>
+          <t>17,05; 21,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 22,78</t>
+          <t>18,27; 22,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 17,95</t>
+          <t>14,01; 18,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,93</t>
+          <t>8,67; 12,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,05; 17,0</t>
+          <t>13,33; 17,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,14</t>
+          <t>6,33; 8,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,08</t>
+          <t>4,33; 6,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,31</t>
+          <t>2,99; 4,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,81</t>
+          <t>4,61; 6,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,46; 18,94</t>
+          <t>16,33; 19,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,28; 13,65</t>
+          <t>11,32; 13,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 10,56</t>
+          <t>8,42; 10,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,04; 34,92</t>
+          <t>13,44; 15,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,79; 13,33</t>
+          <t>11,59; 13,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,61</t>
+          <t>8,14; 9,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 21,05</t>
+          <t>9,4; 10,54</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55215</t>
+          <t>60275</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14242; 34008</t>
+          <t>13742; 32553</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9867; 27808</t>
+          <t>9177; 26247</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3768; 16028</t>
+          <t>3524; 16571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14236; 29730</t>
+          <t>14682; 31666</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19747; 40737</t>
+          <t>20190; 40041</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9279; 26567</t>
+          <t>9072; 25573</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10249; 27404</t>
+          <t>10278; 28039</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26391; 45173</t>
+          <t>29461; 49572</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38565; 66743</t>
+          <t>38662; 67387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22791; 47083</t>
+          <t>21001; 45424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16632; 37374</t>
+          <t>16470; 38232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44361; 69655</t>
+          <t>48212; 75030</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>63005</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8267; 25322</t>
+          <t>8096; 24432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10148; 26993</t>
+          <t>9468; 26910</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5610; 19996</t>
+          <t>5633; 20097</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12967; 28074</t>
+          <t>12855; 29418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14205; 34222</t>
+          <t>15265; 35747</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9224; 24845</t>
+          <t>8308; 23743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7456; 23195</t>
+          <t>7824; 24532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29327; 48166</t>
+          <t>33280; 53853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26316; 51571</t>
+          <t>26371; 51837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21609; 45480</t>
+          <t>21806; 45257</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16380; 38669</t>
+          <t>15686; 38082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46944; 72115</t>
+          <t>51482; 76890</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>56752</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27227; 48956</t>
+          <t>26920; 50401</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34151; 62285</t>
+          <t>32735; 60627</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10245; 26926</t>
+          <t>10249; 26119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7471; 46726</t>
+          <t>18724; 36808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23777; 44828</t>
+          <t>23647; 44491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27233; 51724</t>
+          <t>26731; 51294</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14839; 34816</t>
+          <t>14658; 35307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19609; 35514</t>
+          <t>22145; 41144</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55891; 88074</t>
+          <t>55839; 87630</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66196; 103644</t>
+          <t>67631; 103920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29109; 54479</t>
+          <t>28291; 54552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17836; 78964</t>
+          <t>44739; 72720</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>288960</t>
+          <t>93535</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>357570</t>
+          <t>168753</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110753; 152732</t>
+          <t>111812; 152136</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51593; 85543</t>
+          <t>51226; 83465</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41195; 71004</t>
+          <t>42062; 71058</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55930; 83082</t>
+          <t>62347; 91350</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82152; 118412</t>
+          <t>81315; 117655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30789; 58352</t>
+          <t>31968; 58684</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32328; 59147</t>
+          <t>31992; 59381</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101377; 602721</t>
+          <t>79309; 107631</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>203391; 256388</t>
+          <t>205122; 258637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90980; 131944</t>
+          <t>91642; 135506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80860; 122364</t>
+          <t>80903; 120715</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>162510; 846404</t>
+          <t>145739; 189587</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>148872</t>
+          <t>155205</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>181694</t>
+          <t>189765</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20253; 40722</t>
+          <t>20280; 39492</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18126; 38507</t>
+          <t>18208; 39136</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20622; 40280</t>
+          <t>19906; 40459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23919; 43981</t>
+          <t>24798; 46355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84132; 119446</t>
+          <t>84957; 121556</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94624; 132044</t>
+          <t>93762; 132973</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74395; 111060</t>
+          <t>74206; 111679</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>114463; 176662</t>
+          <t>139648; 173969</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111736; 153121</t>
+          <t>110832; 154129</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118910; 164462</t>
+          <t>118912; 163341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101649; 141872</t>
+          <t>100432; 142903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>145990; 209086</t>
+          <t>169118; 209263</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>149361</t>
+          <t>162137</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>163171</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>780; 8307</t>
+          <t>783; 7440</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>991; 12586</t>
+          <t>994; 10592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3385</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>283096; 342483</t>
+          <t>279162; 340712</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>190741; 244485</t>
+          <t>190385; 246308</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>117522; 167041</t>
+          <t>118361; 163363</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>132730; 166654</t>
+          <t>143491; 183501</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>286126; 352397</t>
+          <t>282614; 345481</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193100; 247027</t>
+          <t>192841; 249692</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115974; 163348</t>
+          <t>118672; 168220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>130402; 169905</t>
+          <t>143864; 183381</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168978</t>
+          <t>179998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>686132</t>
+          <t>521723</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>855110</t>
+          <t>701721</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>209594; 266177</t>
+          <t>207037; 264711</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>150772; 207965</t>
+          <t>148189; 205319</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99298; 146003</t>
+          <t>101148; 145883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129005; 195690</t>
+          <t>158407; 206738</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>555915; 639676</t>
+          <t>551489; 644726</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>399945; 484304</t>
+          <t>401626; 482135</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>298212; 373024</t>
+          <t>297505; 367109</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>499926; 1243666</t>
+          <t>486593; 554878</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>783807; 886243</t>
+          <t>770612; 887124</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>571863; 670004</t>
+          <t>567465; 669785</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>410771; 498185</t>
+          <t>410682; 497782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>635001; 1458652</t>
+          <t>663227; 743753</t>
         </is>
       </c>
     </row>
